--- a/L10_Meeting_Template.xlsx
+++ b/L10_Meeting_Template.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_7CBC4DF2EC16C47FA3E7C059DF9B0089B43B2AF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E17EE3A8-0B97-4B44-9BF7-047E28022A19}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohammadAdib\Documents\GitHub\CompanyTools\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B02E23A-839D-42F4-BB01-713B5DCD71D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L10 Meeting" sheetId="1" r:id="rId1"/>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="125">
   <si>
     <t>TITAN DYNAMICS  —  LEVEL 10 MEETING</t>
   </si>
@@ -317,18 +322,6 @@
     <t>Wk 11</t>
   </si>
   <si>
-    <t>Mission Ready - Raptor</t>
-  </si>
-  <si>
-    <t>Mission Ready - Sparrow</t>
-  </si>
-  <si>
-    <t>Mission Ready - CBAM Quad</t>
-  </si>
-  <si>
-    <t>Sales for Q1 - $1M</t>
-  </si>
-  <si>
     <t>Measurable 5</t>
   </si>
   <si>
@@ -399,13 +392,34 @@
   </si>
   <si>
     <t xml:space="preserve">  OKR #3  —  Key Results</t>
+  </si>
+  <si>
+    <t>Measurable 1</t>
+  </si>
+  <si>
+    <t>Measurable 2</t>
+  </si>
+  <si>
+    <t>Measurable 3</t>
+  </si>
+  <si>
+    <t>Measurable 4</t>
+  </si>
+  <si>
+    <t>OKR 8</t>
+  </si>
+  <si>
+    <t>OKR 9</t>
+  </si>
+  <si>
+    <t>OKR 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +508,12 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -621,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -659,38 +679,64 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -707,29 +753,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1033,7 +1056,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1043,53 +1066,53 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-    </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="36"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="36"/>
-    </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="36"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="36"/>
-    </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="E3" s="15"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="36"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6" ht="8.1" customHeight="1">
+      <c r="E4" s="15"/>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1097,49 +1120,49 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A6" s="29" t="s">
+    <row r="6" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="30" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A8" s="32" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="34"/>
-    </row>
-    <row r="9" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+    </row>
+    <row r="9" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1147,29 +1170,29 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A11" s="29" t="s">
+    <row r="11" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="30" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36"/>
-    </row>
-    <row r="13" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
@@ -1189,10 +1212,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <f>Scorecard!A4</f>
-        <v>Mission Ready - Raptor</v>
+        <v>Measurable 1</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1200,10 +1223,10 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="str">
         <f>Scorecard!A5</f>
-        <v>Mission Ready - Sparrow</v>
+        <v>Measurable 2</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -1211,10 +1234,10 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f>Scorecard!A6</f>
-        <v>Mission Ready - CBAM Quad</v>
+        <v>Measurable 3</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
@@ -1222,10 +1245,10 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="str">
         <f>Scorecard!A7</f>
-        <v>Sales for Q1 - $1M</v>
+        <v>Measurable 4</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
@@ -1233,7 +1256,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <f>Scorecard!A8</f>
         <v>Measurable 5</v>
@@ -1244,7 +1267,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="str">
         <f>Scorecard!A9</f>
         <v>Measurable 6</v>
@@ -1255,7 +1278,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <f>Scorecard!A10</f>
         <v>Measurable 7</v>
@@ -1266,17 +1289,17 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="36"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="16"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1284,29 +1307,29 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="30" t="s">
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1326,7 +1349,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <f>OKRs!B5</f>
         <v>OKR 1</v>
@@ -1337,7 +1360,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <f>OKRs!B6</f>
         <v>OKR 2</v>
@@ -1348,7 +1371,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <f>OKRs!B7</f>
         <v>OKR 3</v>
@@ -1359,7 +1382,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <f>OKRs!B8</f>
         <v>OKR 4</v>
@@ -1370,7 +1393,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <f>OKRs!B9</f>
         <v>OKR 5</v>
@@ -1381,7 +1404,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <f>OKRs!B10</f>
         <v>OKR 6</v>
@@ -1392,17 +1415,17 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="36"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="16"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1410,29 +1433,29 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A34" s="29" t="s">
+    <row r="34" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="30" t="s">
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="36"/>
-    </row>
-    <row r="36" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="16"/>
+    </row>
+    <row r="36" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>29</v>
       </c>
@@ -1452,7 +1475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
@@ -1460,7 +1483,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
@@ -1468,7 +1491,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3"/>
@@ -1476,7 +1499,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
@@ -1484,7 +1507,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="41" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="3"/>
@@ -1492,7 +1515,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="42" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
@@ -1500,7 +1523,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1508,29 +1531,29 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A44" s="29" t="s">
+    <row r="44" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="30" t="s">
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="36"/>
-    </row>
-    <row r="46" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>36</v>
       </c>
@@ -1550,7 +1573,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3"/>
@@ -1558,7 +1581,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="48" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
@@ -1566,7 +1589,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3"/>
@@ -1574,7 +1597,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
@@ -1582,7 +1605,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3"/>
@@ -1590,7 +1613,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -1598,7 +1621,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3"/>
@@ -1606,30 +1629,30 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="16" t="str">
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="35" t="str">
         <f>COUNTIF(D47:D53,"✅ Done")&amp;" / 7 done"</f>
         <v>0 / 7 done</v>
       </c>
-      <c r="F54" s="36"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="19" t="s">
+      <c r="F54" s="16"/>
+    </row>
+    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="35"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="36"/>
-    </row>
-    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="16"/>
+    </row>
+    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1637,29 +1660,29 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A57" s="29" t="s">
+    <row r="57" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="30" t="s">
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A58" s="14" t="s">
+    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="36"/>
-    </row>
-    <row r="59" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="16"/>
+    </row>
+    <row r="59" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
@@ -1679,7 +1702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3"/>
@@ -1687,7 +1710,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="9"/>
@@ -1695,7 +1718,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
     </row>
-    <row r="62" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="62" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3"/>
@@ -1703,7 +1726,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="9"/>
@@ -1711,7 +1734,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
     </row>
-    <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="3"/>
@@ -1719,7 +1742,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="65" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="9"/>
@@ -1727,7 +1750,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
     </row>
-    <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="3"/>
@@ -1735,7 +1758,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
@@ -1743,7 +1766,7 @@
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
     </row>
-    <row r="68" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="3"/>
@@ -1751,7 +1774,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="69" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="9"/>
@@ -1759,7 +1782,7 @@
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
     </row>
-    <row r="70" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="70" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="3"/>
@@ -1767,7 +1790,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="71" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="9"/>
@@ -1775,7 +1798,7 @@
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="72" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="3"/>
@@ -1783,7 +1806,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="73" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="9"/>
@@ -1791,7 +1814,7 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="3"/>
@@ -1799,7 +1822,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="75" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -1807,63 +1830,63 @@
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
     </row>
-    <row r="76" spans="1:6" ht="21.95" customHeight="1">
+    <row r="76" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="38"/>
-    </row>
-    <row r="77" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A77" s="18" t="s">
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B77" s="35"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="36"/>
-    </row>
-    <row r="78" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="16"/>
+    </row>
+    <row r="78" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="16"/>
+    </row>
+    <row r="79" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="16"/>
+    </row>
+    <row r="80" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C80" s="35"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="36"/>
-    </row>
-    <row r="81" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="16"/>
+    </row>
+    <row r="81" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>55</v>
       </c>
@@ -1883,7 +1906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="82" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
@@ -1891,7 +1914,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="9"/>
@@ -1899,7 +1922,7 @@
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
     </row>
-    <row r="84" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="84" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
@@ -1907,7 +1930,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -1915,53 +1938,53 @@
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
     </row>
-    <row r="86" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A86" s="18" t="s">
+    <row r="86" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="36"/>
-    </row>
-    <row r="87" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="16"/>
+    </row>
+    <row r="87" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="36"/>
-    </row>
-    <row r="88" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="16"/>
+    </row>
+    <row r="88" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="36"/>
-    </row>
-    <row r="89" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="16"/>
+    </row>
+    <row r="89" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C89" s="35"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="36"/>
-    </row>
-    <row r="90" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="16"/>
+    </row>
+    <row r="90" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>55</v>
       </c>
@@ -1981,7 +2004,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="91" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
@@ -1989,7 +2012,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="9"/>
@@ -1997,7 +2020,7 @@
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
     </row>
-    <row r="93" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="93" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
@@ -2005,7 +2028,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="94" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2013,53 +2036,53 @@
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
     </row>
-    <row r="95" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A95" s="18" t="s">
+    <row r="95" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B95" s="35"/>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="35"/>
-      <c r="F95" s="36"/>
-    </row>
-    <row r="96" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="16"/>
+    </row>
+    <row r="96" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="36"/>
-    </row>
-    <row r="97" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="16"/>
+    </row>
+    <row r="97" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="36"/>
-    </row>
-    <row r="98" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="16"/>
+    </row>
+    <row r="98" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C98" s="35"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="35"/>
-      <c r="F98" s="36"/>
-    </row>
-    <row r="99" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="16"/>
+    </row>
+    <row r="99" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>55</v>
       </c>
@@ -2079,7 +2102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="100" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
@@ -2087,7 +2110,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="101" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="9"/>
@@ -2095,7 +2118,7 @@
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
     </row>
-    <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
@@ -2103,7 +2126,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="103" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -2111,53 +2134,53 @@
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
     </row>
-    <row r="104" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A104" s="18" t="s">
+    <row r="104" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B104" s="35"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="35"/>
-      <c r="F104" s="36"/>
-    </row>
-    <row r="105" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B104" s="18"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="16"/>
+    </row>
+    <row r="105" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C105" s="35"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="35"/>
-      <c r="F105" s="36"/>
-    </row>
-    <row r="106" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C105" s="18"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="16"/>
+    </row>
+    <row r="106" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C106" s="35"/>
-      <c r="D106" s="35"/>
-      <c r="E106" s="35"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="107" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="16"/>
+    </row>
+    <row r="107" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C107" s="35"/>
-      <c r="D107" s="35"/>
-      <c r="E107" s="35"/>
-      <c r="F107" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="16"/>
+    </row>
+    <row r="108" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>55</v>
       </c>
@@ -2177,7 +2200,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="109" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
@@ -2185,7 +2208,7 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="110" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="9"/>
@@ -2193,7 +2216,7 @@
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
     </row>
-    <row r="111" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="111" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3"/>
@@ -2201,7 +2224,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="112" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -2209,53 +2232,53 @@
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
     </row>
-    <row r="113" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A113" s="18" t="s">
+    <row r="113" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B113" s="35"/>
-      <c r="C113" s="35"/>
-      <c r="D113" s="35"/>
-      <c r="E113" s="35"/>
-      <c r="F113" s="36"/>
-    </row>
-    <row r="114" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="16"/>
+    </row>
+    <row r="114" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C114" s="35"/>
-      <c r="D114" s="35"/>
-      <c r="E114" s="35"/>
-      <c r="F114" s="36"/>
-    </row>
-    <row r="115" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="16"/>
+    </row>
+    <row r="115" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C115" s="35"/>
-      <c r="D115" s="35"/>
-      <c r="E115" s="35"/>
-      <c r="F115" s="36"/>
-    </row>
-    <row r="116" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="16"/>
+    </row>
+    <row r="116" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C116" s="35"/>
-      <c r="D116" s="35"/>
-      <c r="E116" s="35"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="117" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="16"/>
+    </row>
+    <row r="117" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>55</v>
       </c>
@@ -2275,7 +2298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="118" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="3"/>
@@ -2283,7 +2306,7 @@
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="119" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="9"/>
@@ -2291,7 +2314,7 @@
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
     </row>
-    <row r="120" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="120" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="3"/>
@@ -2299,7 +2322,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -2307,53 +2330,53 @@
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
     </row>
-    <row r="122" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A122" s="18" t="s">
+    <row r="122" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B122" s="35"/>
-      <c r="C122" s="35"/>
-      <c r="D122" s="35"/>
-      <c r="E122" s="35"/>
-      <c r="F122" s="36"/>
-    </row>
-    <row r="123" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="16"/>
+    </row>
+    <row r="123" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C123" s="35"/>
-      <c r="D123" s="35"/>
-      <c r="E123" s="35"/>
-      <c r="F123" s="36"/>
-    </row>
-    <row r="124" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="16"/>
+    </row>
+    <row r="124" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C124" s="35"/>
-      <c r="D124" s="35"/>
-      <c r="E124" s="35"/>
-      <c r="F124" s="36"/>
-    </row>
-    <row r="125" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="16"/>
+    </row>
+    <row r="125" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C125" s="35"/>
-      <c r="D125" s="35"/>
-      <c r="E125" s="35"/>
-      <c r="F125" s="36"/>
-    </row>
-    <row r="126" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C125" s="18"/>
+      <c r="D125" s="18"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="16"/>
+    </row>
+    <row r="126" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>55</v>
       </c>
@@ -2373,7 +2396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="127" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="3"/>
@@ -2381,7 +2404,7 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="9"/>
@@ -2389,7 +2412,7 @@
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
     </row>
-    <row r="129" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="129" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="3"/>
@@ -2397,7 +2420,7 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="130" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -2405,53 +2428,53 @@
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
     </row>
-    <row r="131" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A131" s="18" t="s">
+    <row r="131" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B131" s="35"/>
-      <c r="C131" s="35"/>
-      <c r="D131" s="35"/>
-      <c r="E131" s="35"/>
-      <c r="F131" s="36"/>
-    </row>
-    <row r="132" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="16"/>
+    </row>
+    <row r="132" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C132" s="35"/>
-      <c r="D132" s="35"/>
-      <c r="E132" s="35"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="133" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="16"/>
+    </row>
+    <row r="133" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C133" s="35"/>
-      <c r="D133" s="35"/>
-      <c r="E133" s="35"/>
-      <c r="F133" s="36"/>
-    </row>
-    <row r="134" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="16"/>
+    </row>
+    <row r="134" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C134" s="35"/>
-      <c r="D134" s="35"/>
-      <c r="E134" s="35"/>
-      <c r="F134" s="36"/>
-    </row>
-    <row r="135" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="16"/>
+    </row>
+    <row r="135" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>55</v>
       </c>
@@ -2471,7 +2494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="136" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="3"/>
@@ -2479,7 +2502,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="137" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="9"/>
@@ -2487,7 +2510,7 @@
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
     </row>
-    <row r="138" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="138" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="3"/>
@@ -2495,7 +2518,7 @@
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="139" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -2503,53 +2526,53 @@
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
     </row>
-    <row r="140" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A140" s="18" t="s">
+    <row r="140" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B140" s="35"/>
-      <c r="C140" s="35"/>
-      <c r="D140" s="35"/>
-      <c r="E140" s="35"/>
-      <c r="F140" s="36"/>
-    </row>
-    <row r="141" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="16"/>
+    </row>
+    <row r="141" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C141" s="35"/>
-      <c r="D141" s="35"/>
-      <c r="E141" s="35"/>
-      <c r="F141" s="36"/>
-    </row>
-    <row r="142" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="16"/>
+    </row>
+    <row r="142" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C142" s="35"/>
-      <c r="D142" s="35"/>
-      <c r="E142" s="35"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="143" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C142" s="18"/>
+      <c r="D142" s="18"/>
+      <c r="E142" s="18"/>
+      <c r="F142" s="16"/>
+    </row>
+    <row r="143" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C143" s="35"/>
-      <c r="D143" s="35"/>
-      <c r="E143" s="35"/>
-      <c r="F143" s="36"/>
-    </row>
-    <row r="144" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="18"/>
+      <c r="F143" s="16"/>
+    </row>
+    <row r="144" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>55</v>
       </c>
@@ -2569,7 +2592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="145" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="3"/>
@@ -2577,7 +2600,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="146" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="9"/>
@@ -2585,7 +2608,7 @@
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
     </row>
-    <row r="147" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="147" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
@@ -2593,7 +2616,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="148" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -2601,53 +2624,53 @@
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
     </row>
-    <row r="149" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A149" s="18" t="s">
+    <row r="149" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B149" s="35"/>
-      <c r="C149" s="35"/>
-      <c r="D149" s="35"/>
-      <c r="E149" s="35"/>
-      <c r="F149" s="36"/>
-    </row>
-    <row r="150" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B149" s="18"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="18"/>
+      <c r="F149" s="16"/>
+    </row>
+    <row r="150" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C150" s="35"/>
-      <c r="D150" s="35"/>
-      <c r="E150" s="35"/>
-      <c r="F150" s="36"/>
-    </row>
-    <row r="151" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="16"/>
+    </row>
+    <row r="151" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C151" s="35"/>
-      <c r="D151" s="35"/>
-      <c r="E151" s="35"/>
-      <c r="F151" s="36"/>
-    </row>
-    <row r="152" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="16"/>
+    </row>
+    <row r="152" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C152" s="35"/>
-      <c r="D152" s="35"/>
-      <c r="E152" s="35"/>
-      <c r="F152" s="36"/>
-    </row>
-    <row r="153" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C152" s="18"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="18"/>
+      <c r="F152" s="16"/>
+    </row>
+    <row r="153" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>55</v>
       </c>
@@ -2667,7 +2690,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="154" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="3"/>
@@ -2675,7 +2698,7 @@
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="155" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="9"/>
@@ -2683,7 +2706,7 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
     </row>
-    <row r="156" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="156" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="3"/>
@@ -2691,7 +2714,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="157" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -2699,53 +2722,53 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
     </row>
-    <row r="158" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A158" s="18" t="s">
+    <row r="158" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B158" s="35"/>
-      <c r="C158" s="35"/>
-      <c r="D158" s="35"/>
-      <c r="E158" s="35"/>
-      <c r="F158" s="36"/>
-    </row>
-    <row r="159" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B158" s="18"/>
+      <c r="C158" s="18"/>
+      <c r="D158" s="18"/>
+      <c r="E158" s="18"/>
+      <c r="F158" s="16"/>
+    </row>
+    <row r="159" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B159" s="13" t="s">
+      <c r="B159" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C159" s="35"/>
-      <c r="D159" s="35"/>
-      <c r="E159" s="35"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="160" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C159" s="18"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18"/>
+      <c r="F159" s="16"/>
+    </row>
+    <row r="160" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C160" s="35"/>
-      <c r="D160" s="35"/>
-      <c r="E160" s="35"/>
-      <c r="F160" s="36"/>
-    </row>
-    <row r="161" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C160" s="18"/>
+      <c r="D160" s="18"/>
+      <c r="E160" s="18"/>
+      <c r="F160" s="16"/>
+    </row>
+    <row r="161" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B161" s="13" t="s">
+      <c r="B161" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C161" s="35"/>
-      <c r="D161" s="35"/>
-      <c r="E161" s="35"/>
-      <c r="F161" s="36"/>
-    </row>
-    <row r="162" spans="1:6" ht="21.95" customHeight="1">
+      <c r="C161" s="18"/>
+      <c r="D161" s="18"/>
+      <c r="E161" s="18"/>
+      <c r="F161" s="16"/>
+    </row>
+    <row r="162" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>55</v>
       </c>
@@ -2765,7 +2788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="163" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3"/>
@@ -2773,7 +2796,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="164" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="9"/>
@@ -2781,7 +2804,7 @@
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
     </row>
-    <row r="165" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="165" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="3"/>
@@ -2789,7 +2812,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="166" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -2797,7 +2820,7 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
     </row>
-    <row r="167" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="167" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -2805,29 +2828,29 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
     </row>
-    <row r="168" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A168" s="29" t="s">
+    <row r="168" spans="1:6" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B168" s="37"/>
-      <c r="C168" s="37"/>
-      <c r="D168" s="37"/>
-      <c r="E168" s="38"/>
-      <c r="F168" s="30" t="s">
+      <c r="B168" s="23"/>
+      <c r="C168" s="23"/>
+      <c r="D168" s="23"/>
+      <c r="E168" s="24"/>
+      <c r="F168" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A169" s="14" t="s">
+    <row r="169" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="B169" s="35"/>
-      <c r="C169" s="35"/>
-      <c r="D169" s="35"/>
-      <c r="E169" s="35"/>
-      <c r="F169" s="36"/>
-    </row>
-    <row r="170" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B169" s="18"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="18"/>
+      <c r="F169" s="16"/>
+    </row>
+    <row r="170" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>67</v>
       </c>
@@ -2847,7 +2870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="171" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="3"/>
@@ -2855,7 +2878,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="172" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="9"/>
@@ -2863,7 +2886,7 @@
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
     </row>
-    <row r="173" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="173" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="3"/>
@@ -2871,7 +2894,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="174" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="9"/>
@@ -2879,7 +2902,7 @@
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
     </row>
-    <row r="175" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="175" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="3"/>
@@ -2887,7 +2910,7 @@
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="176" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="9"/>
@@ -2895,7 +2918,7 @@
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
     </row>
-    <row r="177" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="177" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="3"/>
@@ -2903,7 +2926,7 @@
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="178" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="9"/>
@@ -2911,7 +2934,7 @@
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
     </row>
-    <row r="179" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="179" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3"/>
@@ -2919,7 +2942,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="180" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="9"/>
@@ -2927,7 +2950,7 @@
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
     </row>
-    <row r="181" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="181" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -2935,17 +2958,17 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
     </row>
-    <row r="182" spans="1:6" ht="21.95" customHeight="1">
+    <row r="182" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B182" s="37"/>
-      <c r="C182" s="37"/>
-      <c r="D182" s="37"/>
-      <c r="E182" s="37"/>
-      <c r="F182" s="38"/>
-    </row>
-    <row r="183" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B182" s="23"/>
+      <c r="C182" s="23"/>
+      <c r="D182" s="23"/>
+      <c r="E182" s="23"/>
+      <c r="F182" s="24"/>
+    </row>
+    <row r="183" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>69</v>
       </c>
@@ -2965,7 +2988,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="184" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="3"/>
@@ -2973,7 +2996,7 @@
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="185" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="9"/>
@@ -2981,7 +3004,7 @@
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
     </row>
-    <row r="186" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="186" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="3"/>
@@ -2989,7 +3012,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="187" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="9"/>
@@ -2997,7 +3020,7 @@
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
     </row>
-    <row r="188" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="188" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="3"/>
@@ -3005,7 +3028,7 @@
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="189" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -3013,17 +3036,17 @@
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
     </row>
-    <row r="190" spans="1:6" ht="21.95" customHeight="1">
+    <row r="190" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B190" s="37"/>
-      <c r="C190" s="37"/>
-      <c r="D190" s="37"/>
-      <c r="E190" s="37"/>
-      <c r="F190" s="38"/>
-    </row>
-    <row r="191" spans="1:6" ht="21.95" customHeight="1">
+      <c r="B190" s="23"/>
+      <c r="C190" s="23"/>
+      <c r="D190" s="23"/>
+      <c r="E190" s="23"/>
+      <c r="F190" s="24"/>
+    </row>
+    <row r="191" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>76</v>
       </c>
@@ -3037,7 +3060,7 @@
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
     </row>
-    <row r="192" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="192" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="3"/>
@@ -3045,7 +3068,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="193" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="9"/>
@@ -3053,7 +3076,7 @@
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
     </row>
-    <row r="194" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="194" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="3"/>
@@ -3061,7 +3084,7 @@
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="195" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="9"/>
@@ -3069,7 +3092,7 @@
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
     </row>
-    <row r="196" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="196" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="3"/>
@@ -3077,7 +3100,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="197" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="9"/>
@@ -3085,7 +3108,7 @@
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
     </row>
-    <row r="198" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="198" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="20" t="s">
         <v>79</v>
       </c>
@@ -3093,12 +3116,12 @@
         <f>IFERROR(AVERAGE(B192:B197),"")</f>
         <v/>
       </c>
-      <c r="C198" s="21"/>
-      <c r="D198" s="35"/>
-      <c r="E198" s="35"/>
-      <c r="F198" s="36"/>
-    </row>
-    <row r="199" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="C198" s="33"/>
+      <c r="D198" s="18"/>
+      <c r="E198" s="18"/>
+      <c r="F198" s="16"/>
+    </row>
+    <row r="199" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -3106,50 +3129,44 @@
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
     </row>
-    <row r="200" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A200" s="22" t="s">
+    <row r="200" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B200" s="39"/>
-      <c r="C200" s="39"/>
-      <c r="D200" s="39"/>
-      <c r="E200" s="39"/>
-      <c r="F200" s="39"/>
+      <c r="B200" s="30"/>
+      <c r="C200" s="30"/>
+      <c r="D200" s="30"/>
+      <c r="E200" s="30"/>
+      <c r="F200" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A168:E168"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A198"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="C198:F198"/>
@@ -3166,32 +3183,38 @@
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="A140:F140"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="A168:E168"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="A169:F169"/>
-    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A58:F58"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" sqref="E14:E20" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3229,48 +3252,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="36"/>
-    </row>
-    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="36"/>
-    </row>
-    <row r="3" spans="1:13" ht="27.95" customHeight="1">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" spans="1:13" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
@@ -3311,9 +3334,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>94</v>
+    <row r="4" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3328,9 +3351,9 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>95</v>
+    <row r="5" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>119</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -3345,9 +3368,9 @@
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>96</v>
+    <row r="6" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3362,9 +3385,9 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="21.95" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>97</v>
+    <row r="7" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -3379,9 +3402,9 @@
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
     </row>
-    <row r="8" spans="1:13" ht="21.95" customHeight="1">
+    <row r="8" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3396,9 +3419,9 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="21.95" customHeight="1">
+    <row r="9" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -3413,9 +3436,9 @@
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
     </row>
-    <row r="10" spans="1:13" ht="21.95" customHeight="1">
+    <row r="10" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3430,9 +3453,9 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="21.95" customHeight="1">
+    <row r="11" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -3447,9 +3470,9 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
     </row>
-    <row r="12" spans="1:13" ht="21.95" customHeight="1">
+    <row r="12" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3464,9 +3487,9 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" ht="21.95" customHeight="1">
+    <row r="13" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -3481,7 +3504,7 @@
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
     </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -3496,22 +3519,22 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
+    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3519,6 +3542,7 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3526,7 +3550,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3536,45 +3560,45 @@
     <col min="7" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-    </row>
-    <row r="4" spans="1:8" ht="27.95" customHeight="1">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>23</v>
@@ -3598,12 +3622,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21.95" customHeight="1">
+    <row r="5" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -3612,12 +3636,12 @@
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="21.95" customHeight="1">
+    <row r="6" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -3626,12 +3650,12 @@
       <c r="G6" s="9"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" ht="21.95" customHeight="1">
+    <row r="7" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -3640,12 +3664,12 @@
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="21.95" customHeight="1">
+    <row r="8" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -3654,12 +3678,12 @@
       <c r="G8" s="9"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" ht="21.95" customHeight="1">
+    <row r="9" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -3668,12 +3692,12 @@
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="21.95" customHeight="1">
+    <row r="10" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -3682,12 +3706,12 @@
       <c r="G10" s="9"/>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="1:8" ht="21.95" customHeight="1">
+    <row r="11" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -3696,11 +3720,13 @@
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="21.95" customHeight="1">
+    <row r="12" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3708,11 +3734,13 @@
       <c r="G12" s="9"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" ht="21.95" customHeight="1">
+    <row r="13" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="13" t="s">
+        <v>123</v>
+      </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -3720,11 +3748,13 @@
       <c r="G13" s="3"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="21.95" customHeight="1">
+    <row r="14" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="13" t="s">
+        <v>124</v>
+      </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3732,7 +3762,7 @@
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3742,42 +3772,42 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
-    </row>
-    <row r="18" spans="1:8" ht="21.95" customHeight="1">
+    <row r="16" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>17</v>
@@ -3792,7 +3822,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3804,7 +3834,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>2</v>
       </c>
@@ -3816,7 +3846,7 @@
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -3828,7 +3858,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3838,30 +3868,30 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36"/>
-    </row>
-    <row r="24" spans="1:8" ht="21.95" customHeight="1">
+    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>17</v>
@@ -3876,7 +3906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -3888,7 +3918,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>2</v>
       </c>
@@ -3900,7 +3930,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -3912,7 +3942,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -3922,30 +3952,30 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="36"/>
-    </row>
-    <row r="30" spans="1:8" ht="21.95" customHeight="1">
+    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>17</v>
@@ -3960,7 +3990,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>1</v>
       </c>
@@ -3972,7 +4002,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>2</v>
       </c>
@@ -3984,7 +4014,7 @@
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>3</v>
       </c>
@@ -3996,7 +4026,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="6" customHeight="1"/>
+    <row r="34" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A3:H3"/>
@@ -4007,6 +4037,7 @@
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="E5:E14" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"🔴 High,🟡 Medium,🟢 Low"</formula1>
@@ -4020,6 +4051,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0df7f343-3985-4f2e-a59f-0a9fbfed1bd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b5d7b36e-83e1-4fd4-8dab-8bf7437cf9c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4DBD3727045E548968B2D7246C91550" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0c7f7afa23d002bb19dcc2cb6ffb603d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="309133ba-e894-457a-a252-d76c370bc267" xmlns:ns3="90c00910-8be4-4468-a61a-5db5f02684d1" xmlns:ns4="0df7f343-3985-4f2e-a59f-0a9fbfed1bd2" xmlns:ns5="b5d7b36e-83e1-4fd4-8dab-8bf7437cf9c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="be88fa919f79ab02b2a8a60b4fc1048c" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="309133ba-e894-457a-a252-d76c370bc267"/>
@@ -4270,34 +4321,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0df7f343-3985-4f2e-a59f-0a9fbfed1bd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b5d7b36e-83e1-4fd4-8dab-8bf7437cf9c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E81E0E98-5552-474E-BBE1-A36A9536C838}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCBA2542-ED56-4814-A955-A834AC10978F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B8B28E6-E08A-4A50-B2CC-8A0D8DF4030B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B8B28E6-E08A-4A50-B2CC-8A0D8DF4030B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0df7f343-3985-4f2e-a59f-0a9fbfed1bd2"/>
+    <ds:schemaRef ds:uri="b5d7b36e-83e1-4fd4-8dab-8bf7437cf9c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCBA2542-ED56-4814-A955-A834AC10978F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E81E0E98-5552-474E-BBE1-A36A9536C838}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="309133ba-e894-457a-a252-d76c370bc267"/>
+    <ds:schemaRef ds:uri="90c00910-8be4-4468-a61a-5db5f02684d1"/>
+    <ds:schemaRef ds:uri="0df7f343-3985-4f2e-a59f-0a9fbfed1bd2"/>
+    <ds:schemaRef ds:uri="b5d7b36e-83e1-4fd4-8dab-8bf7437cf9c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>